--- a/h100price/data/b200_rental_prices.xlsx
+++ b/h100price/data/b200_rental_prices.xlsx
@@ -20220,6 +20220,5704 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G274">
+        <v>6.407407</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J274">
+        <v>1</v>
+      </c>
+      <c r="K274">
+        <v>6.407407</v>
+      </c>
+      <c r="L274">
+        <v>6.407407</v>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38410538,"reliability":0.9617402,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G275">
+        <v>8.463675</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J275">
+        <v>2</v>
+      </c>
+      <c r="K275">
+        <v>4.231838</v>
+      </c>
+      <c r="L275">
+        <v>4.231838</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36081035,"reliability":0.9980898,"location":"Oregon, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G276">
+        <v>8.98433</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J276">
+        <v>1</v>
+      </c>
+      <c r="K276">
+        <v>8.98433</v>
+      </c>
+      <c r="L276">
+        <v>8.98433</v>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210951,"reliability":0.9943645,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G277">
+        <v>12.804843</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J277">
+        <v>2</v>
+      </c>
+      <c r="K277">
+        <v>6.402422</v>
+      </c>
+      <c r="L277">
+        <v>6.402422</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38410542,"reliability":0.9617402,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G278">
+        <v>17.958689</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J278">
+        <v>2</v>
+      </c>
+      <c r="K278">
+        <v>8.979345</v>
+      </c>
+      <c r="L278">
+        <v>8.979345</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210961,"reliability":0.9943645,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G279">
+        <v>20.514904</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J279">
+        <v>4</v>
+      </c>
+      <c r="K279">
+        <v>5.128726</v>
+      </c>
+      <c r="L279">
+        <v>5.128726</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37112599,"reliability":0.9874871,"location":", US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:11Z</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G280">
+        <v>25.599715</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J280">
+        <v>4</v>
+      </c>
+      <c r="K280">
+        <v>6.399929</v>
+      </c>
+      <c r="L280">
+        <v>6.399929</v>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38410539,"reliability":0.9617402,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G281">
+        <v>6.407407</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J281">
+        <v>1</v>
+      </c>
+      <c r="K281">
+        <v>6.407407</v>
+      </c>
+      <c r="L281">
+        <v>6.407407</v>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38410536,"reliability":0.9617909,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G282">
+        <v>8.463675</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J282">
+        <v>2</v>
+      </c>
+      <c r="K282">
+        <v>4.231838</v>
+      </c>
+      <c r="L282">
+        <v>4.231838</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36081035,"reliability":0.998091,"location":"Oregon, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G283">
+        <v>8.98433</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J283">
+        <v>1</v>
+      </c>
+      <c r="K283">
+        <v>8.98433</v>
+      </c>
+      <c r="L283">
+        <v>8.98433</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210951,"reliability":0.9943742,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G284">
+        <v>12.804843</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J284">
+        <v>2</v>
+      </c>
+      <c r="K284">
+        <v>6.402422</v>
+      </c>
+      <c r="L284">
+        <v>6.402422</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38410537,"reliability":0.9617909,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G285">
+        <v>6.407407</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J285">
+        <v>1</v>
+      </c>
+      <c r="K285">
+        <v>6.407407</v>
+      </c>
+      <c r="L285">
+        <v>6.407407</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38410540,"reliability":0.9618431,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G286">
+        <v>8.463675</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J286">
+        <v>2</v>
+      </c>
+      <c r="K286">
+        <v>4.231838</v>
+      </c>
+      <c r="L286">
+        <v>4.231838</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36081035,"reliability":0.998091,"location":"Oregon, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G287">
+        <v>8.98433</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J287">
+        <v>1</v>
+      </c>
+      <c r="K287">
+        <v>8.98433</v>
+      </c>
+      <c r="L287">
+        <v>8.98433</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210951,"reliability":0.9943843,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G288">
+        <v>12.804843</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J288">
+        <v>2</v>
+      </c>
+      <c r="K288">
+        <v>6.402422</v>
+      </c>
+      <c r="L288">
+        <v>6.402422</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38410537,"reliability":0.9618431,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:10Z</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G289">
+        <v>25.599715</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J289">
+        <v>4</v>
+      </c>
+      <c r="K289">
+        <v>6.399929</v>
+      </c>
+      <c r="L289">
+        <v>6.399929</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38410539,"reliability":0.9618431,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G290">
+        <v>4.232906</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J290">
+        <v>1</v>
+      </c>
+      <c r="K290">
+        <v>4.232906</v>
+      </c>
+      <c r="L290">
+        <v>4.232906</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":33945597,"reliability":0.9973221,"location":"Oregon, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G291">
+        <v>13.343305</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J291">
+        <v>2</v>
+      </c>
+      <c r="K291">
+        <v>6.671652</v>
+      </c>
+      <c r="L291">
+        <v>6.671652</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456353,"reliability":0.9618957,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:43Z</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G292">
+        <v>26.676638</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J292">
+        <v>4</v>
+      </c>
+      <c r="K292">
+        <v>6.66916</v>
+      </c>
+      <c r="L292">
+        <v>6.66916</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456349,"reliability":0.9618957,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G293">
+        <v>8.98433</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J293">
+        <v>1</v>
+      </c>
+      <c r="K293">
+        <v>8.98433</v>
+      </c>
+      <c r="L293">
+        <v>8.98433</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210962,"reliability":0.9943945,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G294">
+        <v>4.232906</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J294">
+        <v>1</v>
+      </c>
+      <c r="K294">
+        <v>4.232906</v>
+      </c>
+      <c r="L294">
+        <v>4.232906</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":33945597,"reliability":0.9977998,"location":"Oregon, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G295">
+        <v>8.98433</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J295">
+        <v>1</v>
+      </c>
+      <c r="K295">
+        <v>8.98433</v>
+      </c>
+      <c r="L295">
+        <v>8.98433</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210960,"reliability":0.9944337,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G296">
+        <v>12.317664</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J296">
+        <v>2</v>
+      </c>
+      <c r="K296">
+        <v>6.158832</v>
+      </c>
+      <c r="L296">
+        <v>6.158832</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474455,"reliability":0.7989699,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G297">
+        <v>12.548433</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J297">
+        <v>2</v>
+      </c>
+      <c r="K297">
+        <v>6.274217</v>
+      </c>
+      <c r="L297">
+        <v>6.274217</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456348,"reliability":0.9621007,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G298">
+        <v>12.804843</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J298">
+        <v>2</v>
+      </c>
+      <c r="K298">
+        <v>6.402422</v>
+      </c>
+      <c r="L298">
+        <v>6.402422</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38427002,"reliability":0.9531042,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G299">
+        <v>14.47094</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J299">
+        <v>2</v>
+      </c>
+      <c r="K299">
+        <v>7.23547</v>
+      </c>
+      <c r="L299">
+        <v>7.23547</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466728,"reliability":0.5789482,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G300">
+        <v>14.47094</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J300">
+        <v>2</v>
+      </c>
+      <c r="K300">
+        <v>7.23547</v>
+      </c>
+      <c r="L300">
+        <v>7.23547</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466692,"reliability":0.9715754,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G301">
+        <v>17.958689</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J301">
+        <v>2</v>
+      </c>
+      <c r="K301">
+        <v>8.979345</v>
+      </c>
+      <c r="L301">
+        <v>8.979345</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210961,"reliability":0.9944337,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G302">
+        <v>24.625356</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J302">
+        <v>4</v>
+      </c>
+      <c r="K302">
+        <v>6.156339</v>
+      </c>
+      <c r="L302">
+        <v>6.156339</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474459,"reliability":0.7989699,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G303">
+        <v>25.086895</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J303">
+        <v>4</v>
+      </c>
+      <c r="K303">
+        <v>6.271724</v>
+      </c>
+      <c r="L303">
+        <v>6.271724</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456349,"reliability":0.9621007,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G304">
+        <v>25.599715</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J304">
+        <v>4</v>
+      </c>
+      <c r="K304">
+        <v>6.399929</v>
+      </c>
+      <c r="L304">
+        <v>6.399929</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38427004,"reliability":0.9531042,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G305">
+        <v>28.932479</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J305">
+        <v>4</v>
+      </c>
+      <c r="K305">
+        <v>7.23312</v>
+      </c>
+      <c r="L305">
+        <v>7.23312</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38478157,"reliability":0.9716778,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G306">
+        <v>28.932479</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J306">
+        <v>4</v>
+      </c>
+      <c r="K306">
+        <v>7.23312</v>
+      </c>
+      <c r="L306">
+        <v>7.23312</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466689,"reliability":0.9715754,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G307">
+        <v>28.932479</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J307">
+        <v>4</v>
+      </c>
+      <c r="K307">
+        <v>7.23312</v>
+      </c>
+      <c r="L307">
+        <v>7.23312</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466731,"reliability":0.5789482,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G308">
+        <v>48.2151</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J308">
+        <v>8</v>
+      </c>
+      <c r="K308">
+        <v>6.026887</v>
+      </c>
+      <c r="L308">
+        <v>6.026887</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38478861,"reliability":0.7159844,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G309">
+        <v>49.240741</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J309">
+        <v>8</v>
+      </c>
+      <c r="K309">
+        <v>6.155093</v>
+      </c>
+      <c r="L309">
+        <v>6.155093</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474460,"reliability":0.7989699,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G310">
+        <v>57.855556</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J310">
+        <v>8</v>
+      </c>
+      <c r="K310">
+        <v>7.231944</v>
+      </c>
+      <c r="L310">
+        <v>7.231944</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466534,"reliability":0.9762843,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G311">
+        <v>57.855556</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J311">
+        <v>8</v>
+      </c>
+      <c r="K311">
+        <v>7.231944</v>
+      </c>
+      <c r="L311">
+        <v>7.231944</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38478156,"reliability":0.9716778,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G312">
+        <v>57.855556</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J312">
+        <v>8</v>
+      </c>
+      <c r="K312">
+        <v>7.231944</v>
+      </c>
+      <c r="L312">
+        <v>7.231944</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466694,"reliability":0.9715754,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G313">
+        <v>4.232906</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J313">
+        <v>1</v>
+      </c>
+      <c r="K313">
+        <v>4.232906</v>
+      </c>
+      <c r="L313">
+        <v>4.232906</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":33945590,"reliability":0.9977998,"location":"Oregon, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G314">
+        <v>8.98433</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J314">
+        <v>1</v>
+      </c>
+      <c r="K314">
+        <v>8.98433</v>
+      </c>
+      <c r="L314">
+        <v>8.98433</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210962,"reliability":0.9944337,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G315">
+        <v>12.317664</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J315">
+        <v>2</v>
+      </c>
+      <c r="K315">
+        <v>6.158832</v>
+      </c>
+      <c r="L315">
+        <v>6.158832</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474451,"reliability":0.7989699,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G316">
+        <v>12.548433</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J316">
+        <v>2</v>
+      </c>
+      <c r="K316">
+        <v>6.274217</v>
+      </c>
+      <c r="L316">
+        <v>6.274217</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456353,"reliability":0.9621007,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G317">
+        <v>12.804843</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J317">
+        <v>2</v>
+      </c>
+      <c r="K317">
+        <v>6.402422</v>
+      </c>
+      <c r="L317">
+        <v>6.402422</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38427001,"reliability":0.9531042,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G318">
+        <v>14.47094</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J318">
+        <v>2</v>
+      </c>
+      <c r="K318">
+        <v>7.23547</v>
+      </c>
+      <c r="L318">
+        <v>7.23547</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466730,"reliability":0.5789482,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G319">
+        <v>14.47094</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J319">
+        <v>2</v>
+      </c>
+      <c r="K319">
+        <v>7.23547</v>
+      </c>
+      <c r="L319">
+        <v>7.23547</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466692,"reliability":0.9715754,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G320">
+        <v>17.958689</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J320">
+        <v>2</v>
+      </c>
+      <c r="K320">
+        <v>8.979345</v>
+      </c>
+      <c r="L320">
+        <v>8.979345</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210961,"reliability":0.9944337,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G321">
+        <v>24.625356</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J321">
+        <v>4</v>
+      </c>
+      <c r="K321">
+        <v>6.156339</v>
+      </c>
+      <c r="L321">
+        <v>6.156339</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474459,"reliability":0.7989699,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G322">
+        <v>25.086895</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J322">
+        <v>4</v>
+      </c>
+      <c r="K322">
+        <v>6.271724</v>
+      </c>
+      <c r="L322">
+        <v>6.271724</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38456349,"reliability":0.9621007,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G323">
+        <v>25.599715</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J323">
+        <v>4</v>
+      </c>
+      <c r="K323">
+        <v>6.399929</v>
+      </c>
+      <c r="L323">
+        <v>6.399929</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38427004,"reliability":0.9531042,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G324">
+        <v>28.932479</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J324">
+        <v>4</v>
+      </c>
+      <c r="K324">
+        <v>7.23312</v>
+      </c>
+      <c r="L324">
+        <v>7.23312</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38478157,"reliability":0.9716778,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G325">
+        <v>28.932479</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J325">
+        <v>4</v>
+      </c>
+      <c r="K325">
+        <v>7.23312</v>
+      </c>
+      <c r="L325">
+        <v>7.23312</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466693,"reliability":0.9715754,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G326">
+        <v>28.932479</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J326">
+        <v>4</v>
+      </c>
+      <c r="K326">
+        <v>7.23312</v>
+      </c>
+      <c r="L326">
+        <v>7.23312</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466731,"reliability":0.5789482,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G327">
+        <v>48.2151</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J327">
+        <v>8</v>
+      </c>
+      <c r="K327">
+        <v>6.026887</v>
+      </c>
+      <c r="L327">
+        <v>6.026887</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38478861,"reliability":0.7159844,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G328">
+        <v>49.240741</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J328">
+        <v>8</v>
+      </c>
+      <c r="K328">
+        <v>6.155093</v>
+      </c>
+      <c r="L328">
+        <v>6.155093</v>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474460,"reliability":0.7989699,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G329">
+        <v>57.855556</v>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J329">
+        <v>8</v>
+      </c>
+      <c r="K329">
+        <v>7.231944</v>
+      </c>
+      <c r="L329">
+        <v>7.231944</v>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466534,"reliability":0.9762843,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G330">
+        <v>57.855556</v>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J330">
+        <v>8</v>
+      </c>
+      <c r="K330">
+        <v>7.231944</v>
+      </c>
+      <c r="L330">
+        <v>7.231944</v>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466668,"reliability":0.980468,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:01Z</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G331">
+        <v>57.855556</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J331">
+        <v>8</v>
+      </c>
+      <c r="K331">
+        <v>7.231944</v>
+      </c>
+      <c r="L331">
+        <v>7.231944</v>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466694,"reliability":0.9715754,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G332">
+        <v>8.463675</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J332">
+        <v>2</v>
+      </c>
+      <c r="K332">
+        <v>4.231838</v>
+      </c>
+      <c r="L332">
+        <v>4.231838</v>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36081033,"reliability":0.9980979,"location":"Oregon, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G333">
+        <v>8.98433</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J333">
+        <v>1</v>
+      </c>
+      <c r="K333">
+        <v>8.98433</v>
+      </c>
+      <c r="L333">
+        <v>8.98433</v>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210960,"reliability":0.9944529,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G334">
+        <v>12.061254</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J334">
+        <v>2</v>
+      </c>
+      <c r="K334">
+        <v>6.030627</v>
+      </c>
+      <c r="L334">
+        <v>6.030627</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38478857,"reliability":0.8015487,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G335">
+        <v>12.061254</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J335">
+        <v>2</v>
+      </c>
+      <c r="K335">
+        <v>6.030627</v>
+      </c>
+      <c r="L335">
+        <v>6.030627</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38251606,"reliability":0.9909917,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G336">
+        <v>12.317664</v>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J336">
+        <v>2</v>
+      </c>
+      <c r="K336">
+        <v>6.158832</v>
+      </c>
+      <c r="L336">
+        <v>6.158832</v>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474457,"reliability":0.872764,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G337">
+        <v>14.47094</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J337">
+        <v>2</v>
+      </c>
+      <c r="K337">
+        <v>7.23547</v>
+      </c>
+      <c r="L337">
+        <v>7.23547</v>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466730,"reliability":0.6662647,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G338">
+        <v>14.47094</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J338">
+        <v>2</v>
+      </c>
+      <c r="K338">
+        <v>7.23547</v>
+      </c>
+      <c r="L338">
+        <v>7.23547</v>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466691,"reliability":0.9826975,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G339">
+        <v>17.958689</v>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J339">
+        <v>2</v>
+      </c>
+      <c r="K339">
+        <v>8.979345</v>
+      </c>
+      <c r="L339">
+        <v>8.979345</v>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210961,"reliability":0.9944529,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G340">
+        <v>24.112536</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J340">
+        <v>4</v>
+      </c>
+      <c r="K340">
+        <v>6.028134</v>
+      </c>
+      <c r="L340">
+        <v>6.028134</v>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38251603,"reliability":0.9909917,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G341">
+        <v>24.625356</v>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J341">
+        <v>4</v>
+      </c>
+      <c r="K341">
+        <v>6.156339</v>
+      </c>
+      <c r="L341">
+        <v>6.156339</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474453,"reliability":0.872764,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G342">
+        <v>25.599715</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J342">
+        <v>4</v>
+      </c>
+      <c r="K342">
+        <v>6.399929</v>
+      </c>
+      <c r="L342">
+        <v>6.399929</v>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38427004,"reliability":0.9545506,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G343">
+        <v>28.932479</v>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J343">
+        <v>4</v>
+      </c>
+      <c r="K343">
+        <v>7.23312</v>
+      </c>
+      <c r="L343">
+        <v>7.23312</v>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466670,"reliability":0.9804791,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G344">
+        <v>28.932479</v>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J344">
+        <v>4</v>
+      </c>
+      <c r="K344">
+        <v>7.23312</v>
+      </c>
+      <c r="L344">
+        <v>7.23312</v>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466693,"reliability":0.9826975,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G345">
+        <v>28.932479</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J345">
+        <v>4</v>
+      </c>
+      <c r="K345">
+        <v>7.23312</v>
+      </c>
+      <c r="L345">
+        <v>7.23312</v>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466731,"reliability":0.6662647,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G346">
+        <v>48.2151</v>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J346">
+        <v>8</v>
+      </c>
+      <c r="K346">
+        <v>6.026887</v>
+      </c>
+      <c r="L346">
+        <v>6.026887</v>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38478861,"reliability":0.8015487,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G347">
+        <v>49.240741</v>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J347">
+        <v>8</v>
+      </c>
+      <c r="K347">
+        <v>6.155093</v>
+      </c>
+      <c r="L347">
+        <v>6.155093</v>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474460,"reliability":0.872764,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G348">
+        <v>57.855556</v>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J348">
+        <v>8</v>
+      </c>
+      <c r="K348">
+        <v>7.231944</v>
+      </c>
+      <c r="L348">
+        <v>7.231944</v>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466534,"reliability":0.9850954,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G349">
+        <v>57.855556</v>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J349">
+        <v>8</v>
+      </c>
+      <c r="K349">
+        <v>7.231944</v>
+      </c>
+      <c r="L349">
+        <v>7.231944</v>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466668,"reliability":0.9804791,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G350">
+        <v>57.855556</v>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J350">
+        <v>8</v>
+      </c>
+      <c r="K350">
+        <v>7.231944</v>
+      </c>
+      <c r="L350">
+        <v>7.231944</v>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38466596,"reliability":0.9864626,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/h100price/data/b200_rental_prices.xlsx
+++ b/h100price/data/b200_rental_prices.xlsx
@@ -46934,6 +46934,1930 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G635">
+        <v>4.232906</v>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J635">
+        <v>1</v>
+      </c>
+      <c r="K635">
+        <v>4.232906</v>
+      </c>
+      <c r="L635">
+        <v>4.232906</v>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36083205,"reliability":0.9940458,"location":"Oregon, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G636">
+        <v>6.404558</v>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J636">
+        <v>1</v>
+      </c>
+      <c r="K636">
+        <v>6.404558</v>
+      </c>
+      <c r="L636">
+        <v>6.404558</v>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578327,"reliability":0.9912854,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G637">
+        <v>6.404558</v>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J637">
+        <v>1</v>
+      </c>
+      <c r="K637">
+        <v>6.404558</v>
+      </c>
+      <c r="L637">
+        <v>6.404558</v>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578512,"reliability":0.9065972,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G638">
+        <v>6.404558</v>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J638">
+        <v>1</v>
+      </c>
+      <c r="K638">
+        <v>6.404558</v>
+      </c>
+      <c r="L638">
+        <v>6.404558</v>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578800,"reliability":0.9805823,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G639">
+        <v>8.463675</v>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J639">
+        <v>2</v>
+      </c>
+      <c r="K639">
+        <v>4.231838</v>
+      </c>
+      <c r="L639">
+        <v>4.231838</v>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36083199,"reliability":0.9940458,"location":"Oregon, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>B200 x1</t>
+        </is>
+      </c>
+      <c r="G640">
+        <v>8.98433</v>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J640">
+        <v>1</v>
+      </c>
+      <c r="K640">
+        <v>8.98433</v>
+      </c>
+      <c r="L640">
+        <v>8.98433</v>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37210960,"reliability":0.9945559,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G641">
+        <v>12.061254</v>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J641">
+        <v>2</v>
+      </c>
+      <c r="K641">
+        <v>6.030627</v>
+      </c>
+      <c r="L641">
+        <v>6.030627</v>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38251604,"reliability":0.991192,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G642">
+        <v>12.317664</v>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J642">
+        <v>2</v>
+      </c>
+      <c r="K642">
+        <v>6.158832</v>
+      </c>
+      <c r="L642">
+        <v>6.158832</v>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474451,"reliability":0.897109,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G643">
+        <v>12.801994</v>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J643">
+        <v>2</v>
+      </c>
+      <c r="K643">
+        <v>6.400997</v>
+      </c>
+      <c r="L643">
+        <v>6.400997</v>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578175,"reliability":0.986928,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G644">
+        <v>12.801994</v>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J644">
+        <v>2</v>
+      </c>
+      <c r="K644">
+        <v>6.400997</v>
+      </c>
+      <c r="L644">
+        <v>6.400997</v>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578740,"reliability":0.9915117,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G645">
+        <v>12.801994</v>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J645">
+        <v>2</v>
+      </c>
+      <c r="K645">
+        <v>6.400997</v>
+      </c>
+      <c r="L645">
+        <v>6.400997</v>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578506,"reliability":0.9065972,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>B200 x2</t>
+        </is>
+      </c>
+      <c r="G646">
+        <v>12.804843</v>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J646">
+        <v>2</v>
+      </c>
+      <c r="K646">
+        <v>6.402422</v>
+      </c>
+      <c r="L646">
+        <v>6.402422</v>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38427003,"reliability":0.959067,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G647">
+        <v>18.468483</v>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J647">
+        <v>4</v>
+      </c>
+      <c r="K647">
+        <v>4.617121</v>
+      </c>
+      <c r="L647">
+        <v>4.617121</v>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":30693671,"reliability":0.9940707,"location":", US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G648">
+        <v>20.514904</v>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J648">
+        <v>4</v>
+      </c>
+      <c r="K648">
+        <v>5.128726</v>
+      </c>
+      <c r="L648">
+        <v>5.128726</v>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37112599,"reliability":0.9883259,"location":", US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G649">
+        <v>24.112536</v>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J649">
+        <v>4</v>
+      </c>
+      <c r="K649">
+        <v>6.028134</v>
+      </c>
+      <c r="L649">
+        <v>6.028134</v>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38478856,"reliability":0.8873008,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G650">
+        <v>24.112536</v>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J650">
+        <v>4</v>
+      </c>
+      <c r="K650">
+        <v>6.028134</v>
+      </c>
+      <c r="L650">
+        <v>6.028134</v>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38251607,"reliability":0.991192,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G651">
+        <v>24.625356</v>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J651">
+        <v>4</v>
+      </c>
+      <c r="K651">
+        <v>6.156339</v>
+      </c>
+      <c r="L651">
+        <v>6.156339</v>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474453,"reliability":0.897109,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G652">
+        <v>25.596866</v>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J652">
+        <v>4</v>
+      </c>
+      <c r="K652">
+        <v>6.399217</v>
+      </c>
+      <c r="L652">
+        <v>6.399217</v>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578747,"reliability":0.9915117,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G653">
+        <v>25.596866</v>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J653">
+        <v>4</v>
+      </c>
+      <c r="K653">
+        <v>6.399217</v>
+      </c>
+      <c r="L653">
+        <v>6.399217</v>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578427,"reliability":0.9898933,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>B200 x4</t>
+        </is>
+      </c>
+      <c r="G654">
+        <v>25.596866</v>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J654">
+        <v>4</v>
+      </c>
+      <c r="K654">
+        <v>6.399217</v>
+      </c>
+      <c r="L654">
+        <v>6.399217</v>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578508,"reliability":0.9065972,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G655">
+        <v>36.930021</v>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J655">
+        <v>8</v>
+      </c>
+      <c r="K655">
+        <v>4.616253</v>
+      </c>
+      <c r="L655">
+        <v>4.616253</v>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":30693669,"reliability":0.9940707,"location":", US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G656">
+        <v>48.2151</v>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J656">
+        <v>8</v>
+      </c>
+      <c r="K656">
+        <v>6.026887</v>
+      </c>
+      <c r="L656">
+        <v>6.026887</v>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38478861,"reliability":0.8873008,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G657">
+        <v>48.2151</v>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J657">
+        <v>8</v>
+      </c>
+      <c r="K657">
+        <v>6.026887</v>
+      </c>
+      <c r="L657">
+        <v>6.026887</v>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38251608,"reliability":0.991192,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G658">
+        <v>49.240741</v>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J658">
+        <v>8</v>
+      </c>
+      <c r="K658">
+        <v>6.155093</v>
+      </c>
+      <c r="L658">
+        <v>6.155093</v>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38474460,"reliability":0.897109,"location":"Ohio, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G659">
+        <v>51.18661</v>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J659">
+        <v>8</v>
+      </c>
+      <c r="K659">
+        <v>6.398326</v>
+      </c>
+      <c r="L659">
+        <v>6.398326</v>
+      </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578428,"reliability":0.9898933,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>20260530T135227Z</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>2026-05-30T13:52:28Z</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>B200 x8</t>
+        </is>
+      </c>
+      <c r="G660">
+        <v>51.18661</v>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J660">
+        <v>8</v>
+      </c>
+      <c r="K660">
+        <v>6.398326</v>
+      </c>
+      <c r="L660">
+        <v>6.398326</v>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38578491,"reliability":0.9753666,"location":"Alabama, US"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>